--- a/bom/RB_SWITCH_RevD_JLCPCB_BOM.xlsx
+++ b/bom/RB_SWITCH_RevD_JLCPCB_BOM.xlsx
@@ -403,7 +403,7 @@
           <t>ESP32-S2-MINI-1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>C3013941</t>
         </is>
@@ -422,10 +422,10 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Texas_DRC0010J_ThermalVias</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>Texas_DRC0010J</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>C28060</t>
         </is>
@@ -439,7 +439,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U_CHG</t>
+          <t>U_CHG1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -447,7 +447,7 @@
           <t>SOT-23-5</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>C424093</t>
         </is>
@@ -461,7 +461,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>J_USB</t>
+          <t>J_USB1</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -469,7 +469,7 @@
           <t>USB_C_Receptacle_GCT_USB4105-xx-A_16P_TopMnt_Horizontal</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>C3020560</t>
         </is>
@@ -483,7 +483,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>J_BAT</t>
+          <t>J_BAT1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -491,7 +491,7 @@
           <t>JST_PH_S2B-PH-K_1x02_P2.00mm_Horizontal</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>C173752</t>
         </is>
@@ -513,7 +513,7 @@
           <t>L_Bourns-SRN4018</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>C913207</t>
         </is>
@@ -535,7 +535,7 @@
           <t>LED_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>C2286</t>
         </is>
@@ -557,7 +557,7 @@
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>C22975</t>
         </is>
@@ -579,7 +579,7 @@
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>C21190</t>
         </is>
@@ -601,7 +601,7 @@
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>C23186</t>
         </is>
@@ -623,7 +623,7 @@
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>C25804</t>
         </is>
@@ -645,7 +645,7 @@
           <t>R_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>C25803</t>
         </is>
@@ -667,7 +667,7 @@
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>C19702</t>
         </is>
@@ -689,7 +689,7 @@
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>C59461</t>
         </is>
@@ -711,7 +711,7 @@
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>C15849</t>
         </is>
@@ -733,7 +733,7 @@
           <t>C_0603_1608Metric</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>C14663</t>
         </is>
@@ -747,7 +747,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SW_RST</t>
+          <t>SW_RST1</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
           <t>SW_SPST_B3U-1000P</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>C231329</t>
         </is>
@@ -769,7 +769,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SW_BOOT</t>
+          <t>SW_BOOT1</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
           <t>SW_SPST_B3U-1000P</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>C231329</t>
         </is>
@@ -796,10 +796,10 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SW_TH_Tactile_Omron_B3F-1000</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>SW_TH_Tactile_Omron_B3F-100x</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>C93157</t>
         </is>

--- a/bom/RB_SWITCH_RevD_JLCPCB_BOM.xlsx
+++ b/bom/RB_SWITCH_RevD_JLCPCB_BOM.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C4,C12</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
